--- a/MidiKnob/MidiknobXL_bom.xlsx
+++ b/MidiKnob/MidiknobXL_bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Documents/GitHub/Midi-boards/MidiKnob/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D014EDB7-2ECA-124C-B3EE-3D79C4F677E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039BC502-510D-8A4B-AE29-34E6B04E8D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="920" windowWidth="28040" windowHeight="16440" xr2:uid="{71D61E79-0498-904A-B799-3403509F1DD9}"/>
   </bookViews>
@@ -55,9 +55,6 @@
     <t xml:space="preserve">Resistors: </t>
   </si>
   <si>
-    <t>220 Ohm</t>
-  </si>
-  <si>
     <t>Sockets, switches, housing:</t>
   </si>
   <si>
@@ -142,7 +139,10 @@
     <t>3 pin long header</t>
   </si>
   <si>
-    <t>SPDT switch with middle position</t>
+    <t>SPDT switch ON-OFF-ON</t>
+  </si>
+  <si>
+    <t>100 Ohm</t>
   </si>
 </sst>
 </file>
@@ -692,7 +692,7 @@
   <sheetData>
     <row r="2" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -729,7 +729,7 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3">
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
@@ -772,13 +772,13 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="3">
         <v>2</v>
@@ -787,13 +787,13 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E15" s="3">
         <v>2</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -811,13 +811,13 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
         <v>2</v>
@@ -827,10 +827,10 @@
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="E20" s="3">
         <v>1</v>
@@ -839,13 +839,13 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="E21" s="3">
         <v>1</v>
@@ -855,7 +855,7 @@
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -864,10 +864,10 @@
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="E23" s="3">
         <v>1</v>
@@ -877,10 +877,10 @@
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="3">
         <v>1</v>
@@ -890,7 +890,7 @@
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3">
@@ -901,7 +901,7 @@
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3">
@@ -912,7 +912,7 @@
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3">
@@ -923,7 +923,7 @@
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3">
@@ -932,7 +932,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -948,7 +948,7 @@
     </row>
     <row r="32" spans="1:5" ht="55" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
@@ -957,7 +957,7 @@
     </row>
     <row r="33" spans="1:5" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -966,7 +966,7 @@
     </row>
     <row r="34" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
